--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>465679800</v>
+        <v>3914952000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1186,44 +1186,44 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3914952000</v>
+        <v>465679800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-319180800</v>
+        <v>-946736800</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.64%</t>
+          <t>2.14%→1.76%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-946736800</v>
+        <v>-319180800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2.14%→1.76%</t>
+          <t>0.69%→0.64%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>82→74</t>
         </is>
       </c>
     </row>
@@ -2110,23 +2110,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>46854000</v>
+        <v>72367200</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.47%</t>
+          <t>2.01%→2.26%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2154,23 +2154,23 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>72367200</v>
+        <v>46854000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.26%</t>
+          <t>3.31%→3.47%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-10 ~ 2026-08-18  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-10 ~ 2026-08-18  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3914952000</v>
+        <v>465679800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1478704800</v>
+        <v>3914952000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.93%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>465679800</v>
+        <v>1478704800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>0.57%→0.93%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>23→35</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-872760000</v>
+        <v>-1240566000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.26%→3.45%</t>
+          <t>2.97%→2.59%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>58→55</t>
+          <t>32→29</t>
         </is>
       </c>
     </row>
@@ -1351,23 +1351,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1240566000</v>
+        <v>-872760000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.59%</t>
+          <t>3.26%→3.45%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>32→29</t>
+          <t>58→55</t>
         </is>
       </c>
     </row>
@@ -1721,793 +1721,887 @@
       <c r="K33" s="17" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 14억(4.7%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 10종목  /  매도 11종목</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 82억(2.9%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 8종목  /  매도 12종목</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>872964960</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.32%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>0→116</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-1945828500</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>1.34%→0.58%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>499→224</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>미래에셋벤처투자</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>94</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>1174530000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>0.52%→1.01%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>127→221</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-171</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-2362518900</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>2.35%→1.77%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>521→350</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>5842947600</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>1.47%→3.69%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>50→119</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-145</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-3199077000</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>2.54%→1.24%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>298→153</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>3956988000</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1.50%→2.92%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>69→137</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-130</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-1686539400</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>1.14%→0.57%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>250→120</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티  (신규)</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>90772880</v>
+        <v>558405120</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.32%</t>
+          <t>0.19%→0.42%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>0→122</t>
+          <t>50→97</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-194</v>
+        <v>-119</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-136529440</v>
+        <v>-2667932400</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>7.94%→7.46%</t>
+          <t>1.96%→1.00%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>3,246→3,052</t>
+          <t>241→122</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>노바렉스  (신규)</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>58450080</v>
+        <v>1710601200</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>0.00%→0.63%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>0→51</t>
+          <t>0→33</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-65</v>
+        <v>-70</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-88129600</v>
+        <v>-1149540000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.34%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>349→284</t>
+          <t>70→0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>134793600</v>
+        <v>2784600000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>7.29%→7.76%</t>
+          <t>0.00%→1.02%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>747→795</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>금양그린파워</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-53</v>
+        <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-32183720</v>
+        <v>-1332752400</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.68%</t>
+          <t>5.67%→4.90%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>375→322</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>47364720</v>
+        <v>2798880000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.29%</t>
+          <t>1.66%→2.86%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>646→680</t>
+          <t>25→39</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-43</v>
+        <v>-24</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-34967600</v>
+        <v>-222596640</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.56%</t>
+          <t>0.38%→0.26%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>950→907</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>34242560</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>1.64%→1.76%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>442→474</t>
-        </is>
-      </c>
+      <c r="A46" s="17" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-42</v>
+        <v>-24</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-82832400</v>
+        <v>-1130976000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.43%</t>
+          <t>0.46%→0.00%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>397→355</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>93267200</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>2.80%→3.12%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>138→154</t>
-        </is>
-      </c>
+      <c r="A47" s="17" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>상아프론테크</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-29</v>
+        <v>-23</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-32707360</v>
+        <v>-1826126400</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.31%</t>
+          <t>1.90%→1.37%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>107→78</t>
+          <t>70→47</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>심텍</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>72367200</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>2.01%→2.26%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>72→81</t>
-        </is>
-      </c>
+      <c r="A48" s="17" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-963900000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>1.95%→1.41%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>100→80</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-48632400</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>2.53%→2.36%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>269→251</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>46854000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>3.31%→3.47%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>183→192</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-13</v>
-      </c>
       <c r="I49" s="15" t="n">
-        <v>-39767000</v>
+        <v>-2285085600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>4.55%→4.88%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>61377600</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>2.92%→3.13%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>82→88</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-155268000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>2.64%→2.10%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>44→35</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>12403200</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>0.79%→0.83%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>73→77</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>클래시스</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-24137600</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>0.59%→0.50%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>56→48</t>
-        </is>
-      </c>
+          <t>123→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 48억(2.0%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 6종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-5517600</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>6.26%→6.24%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>980→977</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 20억(3.3%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 4종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>3481719000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>2.63%→4.07%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>400→633</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>일동제약  (편출)</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-400</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-2083520000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.91%→0.00%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>400→0</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>2390472000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>2.41%→3.49%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>201→285</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-156</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-1241136000</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.67%→0.16%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>202→46</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>5603880000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>11.00%→13.34%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>371→453</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-12811200000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>16.15%→10.85%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>356→236</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>554482500</v>
+        <v>1204008000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.56%→3.63%</t>
+          <t>0.91%→1.51%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>368→498</t>
+          <t>99→151</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>HK이노엔  (편출)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
-        <v>-25</v>
+        <v>-102</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-774400000</v>
+        <v>-1442688000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>5.40%→3.54%</t>
+          <t>0.63%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>92→67</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>626247600</v>
+        <v>1675520000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.37%→2.52%</t>
+          <t>5.93%→6.12%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>103→179</t>
+          <t>329→373</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>펩트론  (편출)</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-11</v>
+        <v>-20</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-417934000</v>
+        <v>-1236240000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>9.81%→9.02%</t>
+          <t>0.54%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>150→139</t>
+          <t>20→0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>215289250</v>
+        <v>2443920000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>3.36%→4.10%</t>
+          <t>1.32%→2.63%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>559→614</t>
+          <t>60→100</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
@@ -2516,70 +2610,836 @@
       <c r="J59" s="17" t="n"/>
       <c r="K59" s="17" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 14억(4.7%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 10종목  /  매도 11종목</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>90772880</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.32%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>0→122</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-136529440</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>7.94%→7.46%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>3,246→3,052</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>58450080</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.20%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>0→51</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-88129600</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>1.64%→1.34%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>349→284</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>134793600</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>7.29%→7.76%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>747→795</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-32183720</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.68%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>47364720</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.29%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>646→680</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-34967600</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.68%→2.56%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>34242560</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→1.76%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>442→474</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-82832400</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>2.72%→2.43%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>397→355</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>93267200</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>2.80%→3.12%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>138→154</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-32707360</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.31%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>46854000</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>3.31%→3.47%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-48632400</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>2.53%→2.36%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>269→251</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>72367200</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>2.01%→2.26%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>72→81</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-39767000</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.60%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>69→56</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>61377600</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>2.92%→3.13%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-155268000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>2.64%→2.10%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>44→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>12403200</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>0.79%→0.83%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>73→77</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-24137600</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.50%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>56→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="n"/>
+      <c r="B74" s="17" t="n"/>
+      <c r="C74" s="17" t="n"/>
+      <c r="D74" s="17" t="n"/>
+      <c r="E74" s="17" t="n"/>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-5517600</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>6.26%→6.24%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>980→977</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="19" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 20억(3.3%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>554482500</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>2.56%→3.63%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>-774400000</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→3.54%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>92→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>626247600</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>1.37%→2.52%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>103→179</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>-417934000</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>9.81%→9.02%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>150→139</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>215289250</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>3.36%→4.10%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>559→614</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n"/>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C82" s="11" t="n">
         <v>587079900</v>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>1.96%→3.30%</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>62→89</t>
         </is>
       </c>
-      <c r="G60" s="17" t="n"/>
-      <c r="H60" s="17" t="n"/>
-      <c r="I60" s="17" t="n"/>
-      <c r="J60" s="17" t="n"/>
-      <c r="K60" s="17" t="n"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="G82" s="17" t="n"/>
+      <c r="H82" s="17" t="n"/>
+      <c r="I82" s="17" t="n"/>
+      <c r="J82" s="17" t="n"/>
+      <c r="K82" s="17" t="n"/>
+    </row>
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="19" t="n"/>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="19" t="n"/>
+      <c r="G84" s="19" t="n"/>
+      <c r="H84" s="19" t="n"/>
+      <c r="I84" s="19" t="n"/>
+      <c r="J84" s="19" t="n"/>
+      <c r="K84" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A55:E55"/>
+  <mergeCells count="21">
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="G77:K77"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="G62:K62"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G40:K40"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A54:K54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="G55:K55"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>465679800</v>
+        <v>1478704800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>0.57%→0.93%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>23→35</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3914952000</v>
+        <v>465679800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1186,44 +1186,44 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1478704800</v>
+        <v>3914952000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.93%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-946736800</v>
+        <v>-319180800</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>2.14%→1.76%</t>
+          <t>0.69%→0.64%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>82→74</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-319180800</v>
+        <v>-946736800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.64%</t>
+          <t>2.14%→1.76%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -2966,23 +2966,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>46854000</v>
+        <v>72367200</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.47%</t>
+          <t>2.01%→2.26%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -3010,23 +3010,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>72367200</v>
+        <v>46854000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.26%</t>
+          <t>3.31%→3.47%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,802억   ·   현금 272억(5.5%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 15종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 273억(5.5%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 15종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2846984680</v>
+        <v>2857945160</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2934499650</v>
+        <v>-2945797050</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>126</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1324849680</v>
+        <v>1329950160</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1915864050</v>
+        <v>-1923239850</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>69</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4179585300</v>
+        <v>4195676100</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-49</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1170953000</v>
+        <v>-1175461000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>49</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1456054600</v>
+        <v>1461660200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2381907500</v>
+        <v>-2391077500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>954269550</v>
+        <v>957943350</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3726996900</v>
+        <v>-3741345300</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>432244780</v>
+        <v>433908860</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2359257300</v>
+        <v>-2368340100</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2187510600</v>
+        <v>2195932200</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-26</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-439517780</v>
+        <v>-441209860</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1778248500</v>
+        <v>1785094500</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2888420000</v>
+        <v>-2899540000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>478771200</v>
+        <v>480614400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-19</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1887239600</v>
+        <v>-1894505200</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>969698700</v>
+        <v>973431900</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-956919000</v>
+        <v>-960603000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1478704800</v>
+        <v>3930024000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.93%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2216810400</v>
+        <v>-2225344800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>465679800</v>
+        <v>1484397600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>0.57%→0.93%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>23→35</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>-9</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-825693300</v>
+        <v>-828872100</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3914952000</v>
+        <v>467472600</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-319180800</v>
+        <v>-320409600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>472225500</v>
+        <v>474043500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-946736800</v>
+        <v>-950381600</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2161120000</v>
+        <v>2169440000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-530201700</v>
+        <v>-532242900</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>-3</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1240566000</v>
+        <v>-1245342000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>-3</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-872760000</v>
+        <v>-876120000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,051억   ·   현금 20억(0.5%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 20억(0.5%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1470,7 +1470,7 @@
         <v>106</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>687814920</v>
+        <v>683928960</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>-33</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1995869700</v>
+        <v>-1984593600</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>71</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1219627350</v>
+        <v>1212736800</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>-16</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-2667744000</v>
+        <v>-2652672000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>63</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1251142200</v>
+        <v>1244073600</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>-11</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1174041000</v>
+        <v>-1167408000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>61</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>443756700</v>
+        <v>441249600</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>-7</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1481224500</v>
+        <v>-1472856000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>42</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1875598200</v>
+        <v>1865001600</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1724688000</v>
+        <v>1714944000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1240469100</v>
+        <v>1233460800</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 82억(2.9%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 8종목  /  매도 12종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 83억(2.9%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 8종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1819,7 +1819,7 @@
         <v>116</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>872964960</v>
+        <v>879078160</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>-275</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1945828500</v>
+        <v>-1959454750</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>94</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1174530000</v>
+        <v>1182755000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>-171</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2362518900</v>
+        <v>-2379063150</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>69</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>5842947600</v>
+        <v>5883864600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>-145</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-3199077000</v>
+        <v>-3221479500</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>68</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>3956988000</v>
+        <v>3984698000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>-130</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1686539400</v>
+        <v>-1698349900</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>47</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>558405120</v>
+        <v>562315520</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>-119</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2667932400</v>
+        <v>-2686615400</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>33</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1710601200</v>
+        <v>1722580200</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>-70</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1149540000</v>
+        <v>-1157590000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>15</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2784600000</v>
+        <v>2804100000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1332752400</v>
+        <v>-1342085400</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2798880000</v>
+        <v>2818480000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>-24</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-222596640</v>
+        <v>-224155440</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>-24</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1130976000</v>
+        <v>-1138896000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>-23</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1826126400</v>
+        <v>-1838914400</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>-20</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-963900000</v>
+        <v>-970650000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-2285085600</v>
+        <v>-2301087600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 48억(2.0%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 6종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 48억(2.0%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2372,7 +2372,7 @@
         <v>233</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>3481719000</v>
+        <v>3471478650</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>-400</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2083520000</v>
+        <v>-2077392000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>84</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>2390472000</v>
+        <v>2383441200</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>-156</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1241136000</v>
+        <v>-1237485600</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>82</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>5603880000</v>
+        <v>5587398000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>-120</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-12811200000</v>
+        <v>-12773520000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>52</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1204008000</v>
+        <v>1200466800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>-102</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1442688000</v>
+        <v>-1438444800</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1675520000</v>
+        <v>1670592000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>-20</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1236240000</v>
+        <v>-1232604000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>2443920000</v>
+        <v>2436732000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2709,11 +2709,11 @@
         <v>122</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>90772880</v>
+        <v>88084000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.32%</t>
+          <t>0.00%→0.31%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2730,11 +2730,11 @@
         <v>-194</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-136529440</v>
+        <v>-137414080</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>7.94%→7.46%</t>
+          <t>7.97%→7.50%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2753,7 +2753,7 @@
         <v>51</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>58450080</v>
+        <v>56434560</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
@@ -2774,11 +2774,11 @@
         <v>-65</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-88129600</v>
+        <v>-90303200</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.34%</t>
+          <t>1.68%→1.37%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>7.29%→7.76%</t>
+          <t>7.27%→7.75%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2818,11 +2818,11 @@
         <v>-53</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-32183720</v>
+        <v>-31982320</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.68%</t>
+          <t>0.78%→0.67%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>34</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>47364720</v>
+        <v>48605040</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.29%</t>
+          <t>3.20%→3.37%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2862,11 +2862,11 @@
         <v>-43</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-34967600</v>
+        <v>-36732320</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.56%</t>
+          <t>2.81%→2.69%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2885,11 +2885,11 @@
         <v>32</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>34242560</v>
+        <v>29792000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.64%→1.76%</t>
+          <t>1.43%→1.53%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2906,11 +2906,11 @@
         <v>-42</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-82832400</v>
+        <v>-84428400</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.43%</t>
+          <t>2.77%→2.48%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2929,11 +2929,11 @@
         <v>16</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>93267200</v>
+        <v>88646400</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.80%→3.12%</t>
+          <t>2.65%→2.96%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2950,11 +2950,11 @@
         <v>-29</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-32707360</v>
+        <v>-33236320</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.31%</t>
+          <t>0.43%→0.31%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2973,11 +2973,11 @@
         <v>9</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>72367200</v>
+        <v>74350800</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.26%</t>
+          <t>2.06%→2.32%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2994,11 +2994,11 @@
         <v>-18</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-48632400</v>
+        <v>-50000400</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>2.53%→2.36%</t>
+          <t>2.59%→2.42%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -3017,11 +3017,11 @@
         <v>9</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>46854000</v>
+        <v>46648800</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.47%</t>
+          <t>3.29%→3.45%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -3038,11 +3038,11 @@
         <v>-13</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-39767000</v>
+        <v>-39470600</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>0.73%→0.59%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -3061,11 +3061,11 @@
         <v>6</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>61377600</v>
+        <v>61149600</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.92%→3.13%</t>
+          <t>2.90%→3.11%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -3082,11 +3082,11 @@
         <v>-9</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-155268000</v>
+        <v>-166896000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.10%</t>
+          <t>2.83%→2.25%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -3105,11 +3105,11 @@
         <v>4</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>12403200</v>
+        <v>13026400</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.83%</t>
+          <t>0.82%→0.87%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3126,11 +3126,11 @@
         <v>-8</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-24137600</v>
+        <v>-22800000</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.50%</t>
+          <t>0.55%→0.47%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -3154,11 +3154,11 @@
         <v>-3</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-5517600</v>
+        <v>-5460600</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>6.26%→6.24%</t>
+          <t>6.18%→6.17%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 20억(3.3%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 20억(3.3%)      오늘 2026-08-18  vs  5일전 2026-08-10      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B76" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3930024000</v>
+        <v>467472600</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>467472600</v>
+        <v>3930024000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1484397600</v>
+        <v>3930024000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.57%→0.93%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1186,44 +1186,44 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3930024000</v>
+        <v>1484397600</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.57%→0.93%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>23→35</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-320409600</v>
+        <v>-950381600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.69%→0.64%</t>
+          <t>2.14%→1.76%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-950381600</v>
+        <v>-320409600</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2.14%→1.76%</t>
+          <t>0.69%→0.64%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>82→74</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260818.xlsx
+++ b/reports/pdf_rolling5_20260818.xlsx
@@ -1098,23 +1098,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>467472600</v>
+        <v>3930024000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>5.61%→6.13%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>75→87</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1142,23 +1142,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3930024000</v>
+        <v>467472600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>5.61%→6.13%</t>
+          <t>0.70%→0.89%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>75→87</t>
+          <t>94→106</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1245342000</v>
+        <v>-876120000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.59%</t>
+          <t>3.26%→3.45%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>32→29</t>
+          <t>58→55</t>
         </is>
       </c>
     </row>
@@ -1351,23 +1351,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-876120000</v>
+        <v>-1245342000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>3.26%→3.45%</t>
+          <t>2.97%→2.59%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>58→55</t>
+          <t>32→29</t>
         </is>
       </c>
     </row>
@@ -2141,23 +2141,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-224155440</v>
+        <v>-1138896000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.26%</t>
+          <t>0.46%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2169,23 +2169,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1138896000</v>
+        <v>-224155440</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.00%</t>
+          <t>0.38%→0.26%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
